--- a/ResultadoLatencia.xlsx
+++ b/ResultadoLatencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Diseño de Tics\ANEXOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Diseño de Tics\ANEXOS\DATC_TIC_ANEXOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1371AF50-6D5F-4744-982D-EEC139A77C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80D31CE-82BC-4DAF-A512-AB95F0719A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{4EA6FC55-CD77-4053-A600-627075F256EC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{4EA6FC55-CD77-4053-A600-627075F256EC}"/>
   </bookViews>
   <sheets>
     <sheet name="N1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="22">
   <si>
     <t xml:space="preserve">Nivel de complejidad </t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Tiempo Promedio (ms)</t>
-  </si>
-  <si>
-    <t>Desviación estandar</t>
   </si>
   <si>
     <t>Logica condición</t>
@@ -118,7 +115,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +127,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -157,12 +169,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,8 +208,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -218,19 +230,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -318,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -326,44 +325,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -372,6 +366,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,10 +730,10 @@
   <sheetData>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -734,56 +746,56 @@
       <c r="K3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="31" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="17"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="14"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>2</v>
@@ -792,71 +804,71 @@
         <v>3</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="Q5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="R5" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="15">
         <v>1.3958999999999999</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="11">
         <v>0.58220000000000005</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="16">
         <v>12.1683</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="17">
         <v>6.1169000000000002</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="19">
         <v>18.517700000000001</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="20">
         <v>31.106999999999999</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="21">
         <v>11.7098</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="15">
         <v>2.6657000000000002</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="11">
         <v>0.91479999999999995</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="16">
         <v>16.347799999999999</v>
       </c>
-      <c r="O6" s="20">
+      <c r="O6" s="17">
         <v>11.702500000000001</v>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="19">
         <v>22.126200000000001</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="20">
         <v>18.3565</v>
       </c>
-      <c r="R6" s="24">
+      <c r="R6" s="21">
         <v>14.5684</v>
       </c>
     </row>
@@ -867,22 +879,22 @@
       <c r="B7" s="3">
         <v>1.7537</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="22">
         <v>0.78520000000000001</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="23">
         <v>10.7774</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="18">
         <v>7.7622</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="19">
         <v>15.7273</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="20">
         <v>8.0542999999999996</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="21">
         <v>11.888999999999999</v>
       </c>
       <c r="K7" s="2">
@@ -891,22 +903,22 @@
       <c r="L7" s="3">
         <v>2.1309</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="22">
         <v>1.0628</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="23">
         <v>28.8123</v>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="18">
         <v>5.3581000000000003</v>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="19">
         <v>22.593900000000001</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="20">
         <v>15.788</v>
       </c>
-      <c r="R7" s="24">
+      <c r="R7" s="21">
         <v>12.3467</v>
       </c>
     </row>
@@ -917,22 +929,22 @@
       <c r="B8" s="3">
         <v>1.6329</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="22">
         <v>0.81230000000000002</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="23">
         <v>10.461399999999999</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="18">
         <v>6.7320000000000002</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="19">
         <v>16.7636</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="20">
         <v>8.2646999999999995</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="21">
         <v>12.000400000000001</v>
       </c>
       <c r="K8" s="2">
@@ -941,22 +953,22 @@
       <c r="L8" s="3">
         <v>1.8362000000000001</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="22">
         <v>0.89029999999999998</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="23">
         <v>20.354099999999999</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="18">
         <v>4.6100000000000003</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="19">
         <v>20.087399999999999</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="20">
         <v>11.025399999999999</v>
       </c>
-      <c r="R8" s="24">
+      <c r="R8" s="21">
         <v>14.6022</v>
       </c>
     </row>
@@ -967,22 +979,22 @@
       <c r="B9" s="3">
         <v>3.1705999999999999</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="22">
         <v>0.76829999999999998</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="23">
         <v>10.579499999999999</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="18">
         <v>3.4081000000000001</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="19">
         <v>15.7682</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="20">
         <v>8.2361000000000004</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="21">
         <v>11.887499999999999</v>
       </c>
       <c r="K9" s="2">
@@ -991,22 +1003,22 @@
       <c r="L9" s="3">
         <v>2.1244999999999998</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="22">
         <v>1.0209999999999999</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="23">
         <v>23.052800000000001</v>
       </c>
-      <c r="O9" s="21">
+      <c r="O9" s="18">
         <v>3.97</v>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="19">
         <v>17.0608</v>
       </c>
-      <c r="Q9" s="23">
+      <c r="Q9" s="20">
         <v>18.421099999999999</v>
       </c>
-      <c r="R9" s="24">
+      <c r="R9" s="21">
         <v>11.168799999999999</v>
       </c>
     </row>
@@ -1014,247 +1026,207 @@
       <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="15">
         <v>1.7687999999999999</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="11">
         <v>0.61760000000000004</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="16">
         <v>10.3878</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="17">
         <v>7.2107000000000001</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="24">
         <v>15.561400000000001</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="25">
         <v>8.1740999999999993</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="26">
         <v>11.9781</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="15">
         <v>2.6454</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="11">
         <v>0.15720000000000001</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="16">
         <v>22.156099999999999</v>
       </c>
-      <c r="O10" s="20">
+      <c r="O10" s="17">
         <v>5.0918999999999999</v>
       </c>
-      <c r="P10" s="27">
+      <c r="P10" s="24">
         <v>24.5625</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="25">
         <v>14.880699999999999</v>
       </c>
-      <c r="R10" s="29">
+      <c r="R10" s="26">
         <v>12.969099999999999</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="K11" s="2">
+      <c r="B11" s="38">
+        <f ca="1">AVERAGE(B6:B15)</f>
+        <v>1.94438</v>
+      </c>
+      <c r="C11" s="38">
+        <f ca="1">AVERAGE(C6:C15)</f>
+        <v>0.71311999999999998</v>
+      </c>
+      <c r="D11" s="38">
+        <f ca="1">AVERAGE(D6:D15)</f>
+        <v>10.874879999999999</v>
+      </c>
+      <c r="E11" s="38">
+        <f ca="1">AVERAGE(E6:E15)</f>
+        <v>6.2459800000000003</v>
+      </c>
+      <c r="F11" s="38">
+        <f ca="1">AVERAGE(F6:F15)</f>
+        <v>16.467640000000003</v>
+      </c>
+      <c r="G11" s="38">
+        <f ca="1">AVERAGE(G6:G15)</f>
+        <v>12.767239999999997</v>
+      </c>
+      <c r="H11" s="38">
+        <f ca="1">AVERAGE(H6:H15)</f>
+        <v>11.892959999999999</v>
+      </c>
+      <c r="K11" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="L11" s="39">
+        <f ca="1">AVERAGE(L6:L14)</f>
+        <v>2.2805399999999998</v>
+      </c>
+      <c r="M11" s="39">
+        <f ca="1">AVERAGE(M6:M14)</f>
+        <v>0.80921999999999983</v>
+      </c>
+      <c r="N11" s="39">
+        <f ca="1">AVERAGE(N6:N14)</f>
+        <v>22.14462</v>
+      </c>
+      <c r="O11" s="39">
+        <f ca="1">AVERAGE(O6:O14)</f>
+        <v>6.1464999999999996</v>
+      </c>
+      <c r="P11" s="39">
+        <f ca="1">AVERAGE(P6:P14)</f>
+        <v>21.286160000000002</v>
+      </c>
+      <c r="Q11" s="39">
+        <f ca="1">AVERAGE(Q6:Q14)</f>
+        <v>15.69434</v>
+      </c>
+      <c r="R11" s="39">
+        <f ca="1">AVERAGE(R6:R14)</f>
+        <v>13.131040000000002</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>7</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="K12" s="2">
-        <v>7</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>8</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="K13" s="2">
-        <v>8</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>9</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="K14" s="2">
-        <v>9</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>10</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="K15" s="2">
-        <v>10</v>
-      </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="13">
-        <f>AVERAGE(B6:B15)</f>
-        <v>1.94438</v>
-      </c>
-      <c r="C16" s="13">
-        <f t="shared" ref="C16:H16" si="0">AVERAGE(C6:C15)</f>
-        <v>0.71311999999999998</v>
-      </c>
-      <c r="D16" s="13">
-        <f t="shared" si="0"/>
-        <v>10.874879999999999</v>
-      </c>
-      <c r="E16" s="13">
-        <f t="shared" si="0"/>
-        <v>6.2459800000000003</v>
-      </c>
-      <c r="F16" s="13">
-        <f t="shared" si="0"/>
-        <v>16.467640000000003</v>
-      </c>
-      <c r="G16" s="13">
-        <f t="shared" si="0"/>
-        <v>12.767239999999997</v>
-      </c>
-      <c r="H16" s="13">
-        <f t="shared" si="0"/>
-        <v>11.892959999999999</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L16" s="1">
-        <f>AVERAGE(L6:L14)</f>
-        <v>2.2805399999999998</v>
-      </c>
-      <c r="M16" s="1">
-        <f t="shared" ref="M16:R16" si="1">AVERAGE(M6:M14)</f>
-        <v>0.80921999999999983</v>
-      </c>
-      <c r="N16" s="1">
-        <f t="shared" si="1"/>
-        <v>22.14462</v>
-      </c>
-      <c r="O16" s="1">
-        <f t="shared" si="1"/>
-        <v>6.1464999999999996</v>
-      </c>
-      <c r="P16" s="1">
-        <f t="shared" si="1"/>
-        <v>21.286160000000002</v>
-      </c>
-      <c r="Q16" s="1">
-        <f t="shared" si="1"/>
-        <v>15.69434</v>
-      </c>
-      <c r="R16" s="1">
-        <f t="shared" si="1"/>
-        <v>13.131040000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="K17" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="34"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1280,10 +1252,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -1291,37 +1263,37 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>8</v>
+      <c r="L2" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="J3" s="8"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="J3" s="7"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
     </row>
     <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1331,22 +1303,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>2</v>
@@ -1355,22 +1327,22 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1401,13 +1373,13 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>2.9939</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>2.4190999999999998</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>48.189599999999999</v>
       </c>
       <c r="O5" s="1">
@@ -1577,247 +1549,223 @@
       <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>1.7356</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.15329999999999999</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>8.9144000000000005</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>8.2134</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>15.835100000000001</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>7.0795000000000003</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>9.2274999999999991</v>
       </c>
       <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>2.5413000000000001</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.152</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>25.1434</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>5.2588999999999997</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>24.948899999999998</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>14.447100000000001</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>14.219099999999999</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="K10" s="2">
+      <c r="B10" s="39">
+        <f ca="1">AVERAGE(B5:B14)</f>
+        <v>1.6633</v>
+      </c>
+      <c r="C10" s="39">
+        <f ca="1">AVERAGE(C5:C14)</f>
+        <v>0.60524</v>
+      </c>
+      <c r="D10" s="39">
+        <f ca="1">AVERAGE(D5:D14)</f>
+        <v>7.839500000000001</v>
+      </c>
+      <c r="E10" s="39">
+        <f ca="1">AVERAGE(E5:E14)</f>
+        <v>17.830360000000002</v>
+      </c>
+      <c r="F10" s="39">
+        <f ca="1">AVERAGE(F5:F14)</f>
+        <v>17.157040000000002</v>
+      </c>
+      <c r="G10" s="39">
+        <f ca="1">AVERAGE(G5:G14)</f>
+        <v>10.35946</v>
+      </c>
+      <c r="H10" s="39">
+        <f ca="1">AVERAGE(H5:H14)</f>
+        <v>9.3475000000000001</v>
+      </c>
+      <c r="K10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
+      <c r="L10" s="39">
+        <f ca="1">AVERAGE(L5:L14)</f>
+        <v>2.3392600000000003</v>
+      </c>
+      <c r="M10" s="39">
+        <f ca="1">AVERAGE(M5:M14)</f>
+        <v>1.1918200000000001</v>
+      </c>
+      <c r="N10" s="39">
+        <f ca="1">AVERAGE(N5:N14)</f>
+        <v>38.245799999999996</v>
+      </c>
+      <c r="O10" s="39">
+        <f ca="1">AVERAGE(O5:O14)</f>
+        <v>6.6938000000000004</v>
+      </c>
+      <c r="P10" s="39">
+        <f ca="1">AVERAGE(P5:P14)</f>
+        <v>25.192339999999998</v>
+      </c>
+      <c r="Q10" s="39">
+        <f ca="1">AVERAGE(Q5:Q14)</f>
+        <v>16.652620000000002</v>
+      </c>
+      <c r="R10" s="39">
+        <f ca="1">AVERAGE(R5:R14)</f>
+        <v>16.326919999999998</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="K11" s="2">
-        <v>7</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="K12" s="2">
-        <v>8</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="K13" s="2">
-        <v>9</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="K14" s="2">
-        <v>10</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1">
-        <f>AVERAGE(B5:B14)</f>
-        <v>1.6633</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" ref="C15:H15" si="0">AVERAGE(C5:C14)</f>
-        <v>0.60524</v>
-      </c>
-      <c r="D15" s="1">
-        <f t="shared" si="0"/>
-        <v>7.839500000000001</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>17.830360000000002</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>17.157040000000002</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>10.35946</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="0"/>
-        <v>9.3475000000000001</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <f>AVERAGE(L5:L14)</f>
-        <v>2.3392600000000003</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" ref="M15:R15" si="1">AVERAGE(M5:M14)</f>
-        <v>1.1918200000000001</v>
-      </c>
-      <c r="N15" s="1">
-        <f t="shared" si="1"/>
-        <v>38.245799999999996</v>
-      </c>
-      <c r="O15" s="1">
-        <f t="shared" si="1"/>
-        <v>6.6938000000000004</v>
-      </c>
-      <c r="P15" s="1">
-        <f t="shared" si="1"/>
-        <v>25.192339999999998</v>
-      </c>
-      <c r="Q15" s="1">
-        <f t="shared" si="1"/>
-        <v>16.652620000000002</v>
-      </c>
-      <c r="R15" s="1">
-        <f t="shared" si="1"/>
-        <v>16.326919999999998</v>
-      </c>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="K16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1844,73 +1792,73 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
+      <c r="B2" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>11</v>
+      <c r="L2" s="9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="J3" s="8"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="J3" s="7"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
     </row>
     <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="41" t="s">
         <v>16</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>2</v>
@@ -1919,71 +1867,71 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="3">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="22">
         <v>0.65849999999999997</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="23">
         <v>7.9059999999999997</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="18">
         <v>14.7172</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="19">
         <v>13.020200000000001</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="20">
         <v>6.2733999999999996</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="21">
         <v>8.1717999999999993</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="3">
         <v>2.3540999999999999</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="22">
         <v>1.095</v>
       </c>
-      <c r="N5" s="19">
+      <c r="N5" s="23">
         <v>20.732700000000001</v>
       </c>
-      <c r="O5" s="21">
+      <c r="O5" s="18">
         <v>4.7975000000000003</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="19">
         <v>27.687899999999999</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="20">
         <v>17.489999999999998</v>
       </c>
-      <c r="R5" s="24">
+      <c r="R5" s="21">
         <v>18.153600000000001</v>
       </c>
     </row>
@@ -1994,22 +1942,22 @@
       <c r="B6" s="3">
         <v>1.1012</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="22">
         <v>0.6573</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="23">
         <v>8.2474000000000007</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="18">
         <v>5.2853000000000003</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="19">
         <v>13.045199999999999</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="20">
         <v>7.1315999999999997</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="21">
         <v>8.1466999999999992</v>
       </c>
       <c r="K6" s="2">
@@ -2018,22 +1966,22 @@
       <c r="L6" s="3">
         <v>2.2862</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="22">
         <v>1.1796</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="23">
         <v>22.037099999999999</v>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="18">
         <v>3.8780000000000001</v>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="19">
         <v>23.6629</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="20">
         <v>17.674600000000002</v>
       </c>
-      <c r="R6" s="24">
+      <c r="R6" s="21">
         <v>17.1616</v>
       </c>
     </row>
@@ -2044,22 +1992,22 @@
       <c r="B7" s="3">
         <v>1.1694</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="22">
         <v>0.62960000000000005</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="23">
         <v>9.1356999999999999</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="18">
         <v>10.0069</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="19">
         <v>12.9671</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="20">
         <v>5.9476000000000004</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="21">
         <v>8.2449999999999992</v>
       </c>
       <c r="K7" s="2">
@@ -2068,22 +2016,22 @@
       <c r="L7" s="3">
         <v>2.3336000000000001</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="22">
         <v>2.0857999999999999</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="23">
         <v>36.124600000000001</v>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="18">
         <v>4.4275000000000002</v>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="19">
         <v>24.488499999999998</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="20">
         <v>19.728400000000001</v>
       </c>
-      <c r="R7" s="24">
+      <c r="R7" s="21">
         <v>13.382400000000001</v>
       </c>
     </row>
@@ -2094,22 +2042,22 @@
       <c r="B8" s="3">
         <v>1.8751</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="22">
         <v>0.62990000000000002</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="23">
         <v>7.8061999999999996</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="18">
         <v>10.1991</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="19">
         <v>13.1244</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="20">
         <v>5.9614000000000003</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="21">
         <v>8.4032999999999998</v>
       </c>
       <c r="K8" s="2">
@@ -2118,22 +2066,22 @@
       <c r="L8" s="3">
         <v>2.3645</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="22">
         <v>1.0427999999999999</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="23">
         <v>37.915599999999998</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="18">
         <v>4.9729000000000001</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="19">
         <v>25.014399999999998</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="20">
         <v>22.292899999999999</v>
       </c>
-      <c r="R8" s="24">
+      <c r="R8" s="21">
         <v>18.8231</v>
       </c>
     </row>
@@ -2141,247 +2089,223 @@
       <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="3">
         <v>0.95799999999999996</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="22">
         <v>0.13900000000000001</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="23">
         <v>7.8360000000000003</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="18">
         <v>3.9799000000000002</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="19">
         <v>13.1616</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="20">
         <v>5.8539000000000003</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="21">
         <v>8.3143999999999991</v>
       </c>
       <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="3">
         <v>2.4691000000000001</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="22">
         <v>0.15079999999999999</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="23">
         <v>20.605399999999999</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="18">
         <v>4.1925999999999997</v>
       </c>
-      <c r="P9" s="27">
+      <c r="P9" s="19">
         <v>26.9711</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="20">
         <v>30.151499999999999</v>
       </c>
-      <c r="R9" s="29">
+      <c r="R9" s="21">
         <v>21.028700000000001</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="K10" s="2">
+      <c r="B10" s="39">
+        <f ca="1">AVERAGE(B5:B14)</f>
+        <v>1.2387400000000002</v>
+      </c>
+      <c r="C10" s="39">
+        <f ca="1">AVERAGE(C5:C14)</f>
+        <v>0.5428599999999999</v>
+      </c>
+      <c r="D10" s="39">
+        <f ca="1">AVERAGE(D5:D14)</f>
+        <v>8.1862600000000008</v>
+      </c>
+      <c r="E10" s="39">
+        <f ca="1">AVERAGE(E5:E14)</f>
+        <v>8.8376800000000006</v>
+      </c>
+      <c r="F10" s="39">
+        <f ca="1">AVERAGE(F5:F14)</f>
+        <v>13.063700000000001</v>
+      </c>
+      <c r="G10" s="39">
+        <f ca="1">AVERAGE(G5:G14)</f>
+        <v>6.2335799999999999</v>
+      </c>
+      <c r="H10" s="39">
+        <f ca="1">AVERAGE(H5:H14)</f>
+        <v>8.25624</v>
+      </c>
+      <c r="K10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
+      <c r="L10" s="39">
+        <f ca="1">AVERAGE(L5:L14)</f>
+        <v>2.3615000000000004</v>
+      </c>
+      <c r="M10" s="39">
+        <f ca="1">AVERAGE(M5:M14)</f>
+        <v>1.1108</v>
+      </c>
+      <c r="N10" s="39">
+        <f ca="1">AVERAGE(N5:N14)</f>
+        <v>27.483080000000001</v>
+      </c>
+      <c r="O10" s="39">
+        <f ca="1">AVERAGE(O5:O14)</f>
+        <v>4.4536999999999995</v>
+      </c>
+      <c r="P10" s="39">
+        <f ca="1">AVERAGE(P5:P14)</f>
+        <v>25.564959999999996</v>
+      </c>
+      <c r="Q10" s="39">
+        <f ca="1">AVERAGE(Q5:Q14)</f>
+        <v>21.467480000000002</v>
+      </c>
+      <c r="R10" s="39">
+        <f ca="1">AVERAGE(R5:R14)</f>
+        <v>17.709880000000002</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="K11" s="2">
-        <v>7</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="K12" s="2">
-        <v>8</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="K13" s="2">
-        <v>9</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="K14" s="2">
-        <v>10</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1">
-        <f>AVERAGE(B5:B14)</f>
-        <v>1.2387400000000002</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" ref="C15:H15" si="0">AVERAGE(C5:C14)</f>
-        <v>0.5428599999999999</v>
-      </c>
-      <c r="D15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.1862600000000008</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.8376800000000006</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>13.063700000000001</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>6.2335799999999999</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.25624</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <f>AVERAGE(L5:L14)</f>
-        <v>2.3615000000000004</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" ref="M15:R15" si="1">AVERAGE(M5:M14)</f>
-        <v>1.1108</v>
-      </c>
-      <c r="N15" s="1">
-        <f t="shared" si="1"/>
-        <v>27.483080000000001</v>
-      </c>
-      <c r="O15" s="1">
-        <f t="shared" si="1"/>
-        <v>4.4536999999999995</v>
-      </c>
-      <c r="P15" s="1">
-        <f t="shared" si="1"/>
-        <v>25.564959999999996</v>
-      </c>
-      <c r="Q15" s="1">
-        <f t="shared" si="1"/>
-        <v>21.467480000000002</v>
-      </c>
-      <c r="R15" s="1">
-        <f t="shared" si="1"/>
-        <v>17.709880000000002</v>
-      </c>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="K16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2407,48 +2331,48 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>12</v>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>12</v>
+      <c r="L2" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="J3" s="8"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="J3" s="7"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
     </row>
     <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2458,22 +2382,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>2</v>
@@ -2482,22 +2406,22 @@
         <v>3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="R4" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -2510,7 +2434,7 @@
       <c r="C5" s="1">
         <v>0.56259999999999999</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>9.5022000000000002</v>
       </c>
       <c r="E5" s="1">
@@ -2528,13 +2452,13 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>3.5044</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>1.1186</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>34.637099999999997</v>
       </c>
       <c r="O5" s="1">
@@ -2704,247 +2628,223 @@
       <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>1.1206</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.15090000000000001</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>7.8193000000000001</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>12.9833</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>12.2437</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>5.5430000000000001</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>7.5948000000000002</v>
       </c>
       <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>1.9164000000000001</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>0.14860000000000001</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>39.022799999999997</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>7.1577000000000002</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>22.207999999999998</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>16.803899999999999</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>13.658099999999999</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="K10" s="2">
+      <c r="B10" s="39">
+        <f ca="1">AVERAGE(B5:B14)</f>
+        <v>1.4054600000000002</v>
+      </c>
+      <c r="C10" s="39">
+        <f ca="1">AVERAGE(C5:C14)</f>
+        <v>0.4966000000000001</v>
+      </c>
+      <c r="D10" s="39">
+        <f ca="1">AVERAGE(D5:D14)</f>
+        <v>7.9158599999999995</v>
+      </c>
+      <c r="E10" s="39">
+        <f ca="1">AVERAGE(E5:E14)</f>
+        <v>23.38964</v>
+      </c>
+      <c r="F10" s="39">
+        <f ca="1">AVERAGE(F5:F14)</f>
+        <v>12.645860000000003</v>
+      </c>
+      <c r="G10" s="39">
+        <f ca="1">AVERAGE(G5:G14)</f>
+        <v>6.0935000000000006</v>
+      </c>
+      <c r="H10" s="39">
+        <f ca="1">AVERAGE(H5:H14)</f>
+        <v>7.6197600000000012</v>
+      </c>
+      <c r="K10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
+      <c r="L10" s="39">
+        <f ca="1">AVERAGE(L5:L14)</f>
+        <v>2.5003799999999998</v>
+      </c>
+      <c r="M10" s="39">
+        <f ca="1">AVERAGE(M5:M14)</f>
+        <v>1.2528599999999999</v>
+      </c>
+      <c r="N10" s="39">
+        <f ca="1">AVERAGE(N5:N14)</f>
+        <v>26.216259999999998</v>
+      </c>
+      <c r="O10" s="39">
+        <f ca="1">AVERAGE(O5:O14)</f>
+        <v>6.1052400000000002</v>
+      </c>
+      <c r="P10" s="39">
+        <f ca="1">AVERAGE(P5:P14)</f>
+        <v>27.358699999999999</v>
+      </c>
+      <c r="Q10" s="39">
+        <f ca="1">AVERAGE(Q5:Q14)</f>
+        <v>17.412479999999999</v>
+      </c>
+      <c r="R10" s="39">
+        <f ca="1">AVERAGE(R5:R14)</f>
+        <v>16.238660000000003</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="K11" s="2">
-        <v>7</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="K12" s="2">
-        <v>8</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="K13" s="2">
-        <v>9</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="K14" s="2">
-        <v>10</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1">
-        <f>AVERAGE(B5:B14)</f>
-        <v>1.4054600000000002</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" ref="C15:H15" si="0">AVERAGE(C5:C14)</f>
-        <v>0.4966000000000001</v>
-      </c>
-      <c r="D15" s="1">
-        <f t="shared" si="0"/>
-        <v>7.9158599999999995</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>23.38964</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>12.645860000000003</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>6.0935000000000006</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="0"/>
-        <v>7.6197600000000012</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <f>AVERAGE(L5:L14)</f>
-        <v>2.5003799999999998</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" ref="M15:R15" si="1">AVERAGE(M5:M14)</f>
-        <v>1.2528599999999999</v>
-      </c>
-      <c r="N15" s="1">
-        <f t="shared" si="1"/>
-        <v>26.216259999999998</v>
-      </c>
-      <c r="O15" s="1">
-        <f t="shared" si="1"/>
-        <v>6.1052400000000002</v>
-      </c>
-      <c r="P15" s="1">
-        <f t="shared" si="1"/>
-        <v>27.358699999999999</v>
-      </c>
-      <c r="Q15" s="1">
-        <f t="shared" si="1"/>
-        <v>17.412479999999999</v>
-      </c>
-      <c r="R15" s="1">
-        <f t="shared" si="1"/>
-        <v>16.238660000000003</v>
-      </c>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="K16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2965,78 +2865,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="A1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="30">
-        <f>'N1'!B16</f>
+      <c r="C3" s="27">
+        <f ca="1">'N1'!B11</f>
         <v>1.94438</v>
       </c>
-      <c r="D3" s="30">
-        <f>'N1'!C16</f>
+      <c r="D3" s="27">
+        <f ca="1">'N1'!C11</f>
         <v>0.71311999999999998</v>
       </c>
-      <c r="E3" s="30">
-        <f>'N1'!D16</f>
+      <c r="E3" s="27">
+        <f ca="1">'N1'!D11</f>
         <v>10.874879999999999</v>
       </c>
-      <c r="F3" s="30">
-        <f>'N1'!E16</f>
+      <c r="F3" s="27">
+        <f ca="1">'N1'!E11</f>
         <v>6.2459800000000003</v>
       </c>
-      <c r="G3" s="30">
-        <f>'N1'!F16</f>
+      <c r="G3" s="27">
+        <f ca="1">'N1'!F11</f>
         <v>16.467640000000003</v>
       </c>
-      <c r="H3" s="30">
-        <f>'N1'!G16</f>
+      <c r="H3" s="27">
+        <f ca="1">'N1'!G11</f>
         <v>12.767239999999997</v>
       </c>
-      <c r="I3" s="30">
-        <f>'N1'!H16</f>
+      <c r="I3" s="27">
+        <f ca="1">'N1'!H11</f>
         <v>11.892959999999999</v>
       </c>
     </row>
@@ -3044,32 +2944,32 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="30">
-        <f>'N2'!B15</f>
+      <c r="C4" s="27">
+        <f ca="1">'N2'!B10</f>
         <v>1.6633</v>
       </c>
-      <c r="D4" s="30">
-        <f>'N2'!C15</f>
+      <c r="D4" s="27">
+        <f ca="1">'N2'!C10</f>
         <v>0.60524</v>
       </c>
-      <c r="E4" s="30">
-        <f>'N2'!D15</f>
+      <c r="E4" s="27">
+        <f ca="1">'N2'!D10</f>
         <v>7.839500000000001</v>
       </c>
-      <c r="F4" s="30">
-        <f>'N2'!E15</f>
+      <c r="F4" s="27">
+        <f ca="1">'N2'!E10</f>
         <v>17.830360000000002</v>
       </c>
-      <c r="G4" s="30">
-        <f>'N2'!F15</f>
+      <c r="G4" s="27">
+        <f ca="1">'N2'!F10</f>
         <v>17.157040000000002</v>
       </c>
-      <c r="H4" s="30">
-        <f>'N2'!G15</f>
+      <c r="H4" s="27">
+        <f ca="1">'N2'!G10</f>
         <v>10.35946</v>
       </c>
-      <c r="I4" s="30">
-        <f>'N2'!H15</f>
+      <c r="I4" s="27">
+        <f ca="1">'N2'!H10</f>
         <v>9.3475000000000001</v>
       </c>
     </row>
@@ -3077,32 +2977,32 @@
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="30">
-        <f>'N3'!B15</f>
+      <c r="C5" s="27">
+        <f ca="1">'N3'!B10</f>
         <v>1.2387400000000002</v>
       </c>
-      <c r="D5" s="30">
-        <f>'N3'!C15</f>
+      <c r="D5" s="27">
+        <f ca="1">'N3'!C10</f>
         <v>0.5428599999999999</v>
       </c>
-      <c r="E5" s="30">
-        <f>'N3'!D15</f>
+      <c r="E5" s="27">
+        <f ca="1">'N3'!D10</f>
         <v>8.1862600000000008</v>
       </c>
-      <c r="F5" s="30">
-        <f>'N3'!E15</f>
+      <c r="F5" s="27">
+        <f ca="1">'N3'!E10</f>
         <v>8.8376800000000006</v>
       </c>
-      <c r="G5" s="30">
-        <f>'N3'!F15</f>
+      <c r="G5" s="27">
+        <f ca="1">'N3'!F10</f>
         <v>13.063700000000001</v>
       </c>
-      <c r="H5" s="30">
-        <f>'N3'!G15</f>
+      <c r="H5" s="27">
+        <f ca="1">'N3'!G10</f>
         <v>6.2335799999999999</v>
       </c>
-      <c r="I5" s="30">
-        <f>'N3'!H15</f>
+      <c r="I5" s="27">
+        <f ca="1">'N3'!H10</f>
         <v>8.25624</v>
       </c>
     </row>
@@ -3110,94 +3010,94 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="30">
-        <f>'N4'!B15</f>
+      <c r="C6" s="27">
+        <f ca="1">'N4'!B10</f>
         <v>1.4054600000000002</v>
       </c>
-      <c r="D6" s="30">
-        <f>'N4'!C15</f>
+      <c r="D6" s="27">
+        <f ca="1">'N4'!C10</f>
         <v>0.4966000000000001</v>
       </c>
-      <c r="E6" s="30">
-        <f>'N4'!D15</f>
+      <c r="E6" s="27">
+        <f ca="1">'N4'!D10</f>
         <v>7.9158599999999995</v>
       </c>
-      <c r="F6" s="30">
-        <f>'N4'!E15</f>
+      <c r="F6" s="27">
+        <f ca="1">'N4'!E10</f>
         <v>23.38964</v>
       </c>
-      <c r="G6" s="30">
-        <f>'N4'!F15</f>
+      <c r="G6" s="27">
+        <f ca="1">'N4'!F10</f>
         <v>12.645860000000003</v>
       </c>
-      <c r="H6" s="30">
-        <f>'N4'!G15</f>
+      <c r="H6" s="27">
+        <f ca="1">'N4'!G10</f>
         <v>6.0935000000000006</v>
       </c>
-      <c r="I6" s="30">
-        <f>'N4'!H15</f>
+      <c r="I6" s="27">
+        <f ca="1">'N4'!H10</f>
         <v>7.6197600000000012</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="I9" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="30">
-        <f>'N1'!L16</f>
+      <c r="C10" s="27">
+        <f ca="1">'N1'!L11</f>
         <v>2.2805399999999998</v>
       </c>
-      <c r="D10" s="30">
-        <f>'N1'!M16</f>
+      <c r="D10" s="27">
+        <f ca="1">'N1'!M11</f>
         <v>0.80921999999999983</v>
       </c>
-      <c r="E10" s="30">
-        <f>'N1'!N16</f>
+      <c r="E10" s="27">
+        <f ca="1">'N1'!N11</f>
         <v>22.14462</v>
       </c>
-      <c r="F10" s="30">
-        <f>'N1'!O16</f>
+      <c r="F10" s="27">
+        <f ca="1">'N1'!O11</f>
         <v>6.1464999999999996</v>
       </c>
-      <c r="G10" s="30">
-        <f>'N1'!P16</f>
+      <c r="G10" s="27">
+        <f ca="1">'N1'!P11</f>
         <v>21.286160000000002</v>
       </c>
-      <c r="H10" s="30">
-        <f>'N1'!Q16</f>
+      <c r="H10" s="27">
+        <f ca="1">'N1'!Q11</f>
         <v>15.69434</v>
       </c>
-      <c r="I10" s="30">
-        <f>'N1'!R16</f>
+      <c r="I10" s="27">
+        <f ca="1">'N1'!R11</f>
         <v>13.131040000000002</v>
       </c>
     </row>
@@ -3205,32 +3105,32 @@
       <c r="B11" s="1">
         <v>2</v>
       </c>
-      <c r="C11" s="30">
-        <f>'N2'!L15</f>
+      <c r="C11" s="27">
+        <f ca="1">'N2'!L10</f>
         <v>2.3392600000000003</v>
       </c>
-      <c r="D11" s="30">
-        <f>'N2'!M15</f>
+      <c r="D11" s="27">
+        <f ca="1">'N2'!M10</f>
         <v>1.1918200000000001</v>
       </c>
-      <c r="E11" s="30">
-        <f>'N2'!N15</f>
+      <c r="E11" s="27">
+        <f ca="1">'N2'!N10</f>
         <v>38.245799999999996</v>
       </c>
-      <c r="F11" s="30">
-        <f>'N2'!O15</f>
+      <c r="F11" s="27">
+        <f ca="1">'N2'!O10</f>
         <v>6.6938000000000004</v>
       </c>
-      <c r="G11" s="30">
-        <f>'N2'!P15</f>
+      <c r="G11" s="27">
+        <f ca="1">'N2'!P10</f>
         <v>25.192339999999998</v>
       </c>
-      <c r="H11" s="30">
-        <f>'N2'!Q15</f>
+      <c r="H11" s="27">
+        <f ca="1">'N2'!Q10</f>
         <v>16.652620000000002</v>
       </c>
-      <c r="I11" s="30">
-        <f>'N2'!R15</f>
+      <c r="I11" s="27">
+        <f ca="1">'N2'!R10</f>
         <v>16.326919999999998</v>
       </c>
     </row>
@@ -3238,32 +3138,32 @@
       <c r="B12" s="1">
         <v>3</v>
       </c>
-      <c r="C12" s="30">
-        <f>'N3'!L15</f>
+      <c r="C12" s="27">
+        <f ca="1">'N3'!L10</f>
         <v>2.3615000000000004</v>
       </c>
-      <c r="D12" s="30">
-        <f>'N3'!M15</f>
+      <c r="D12" s="27">
+        <f ca="1">'N3'!M10</f>
         <v>1.1108</v>
       </c>
-      <c r="E12" s="30">
-        <f>'N3'!N15</f>
+      <c r="E12" s="27">
+        <f ca="1">'N3'!N10</f>
         <v>27.483080000000001</v>
       </c>
-      <c r="F12" s="30">
-        <f>'N3'!O15</f>
+      <c r="F12" s="27">
+        <f ca="1">'N3'!O10</f>
         <v>4.4536999999999995</v>
       </c>
-      <c r="G12" s="30">
-        <f>'N3'!P15</f>
+      <c r="G12" s="27">
+        <f ca="1">'N3'!P10</f>
         <v>25.564959999999996</v>
       </c>
-      <c r="H12" s="30">
-        <f>'N3'!Q15</f>
+      <c r="H12" s="27">
+        <f ca="1">'N3'!Q10</f>
         <v>21.467480000000002</v>
       </c>
-      <c r="I12" s="30">
-        <f>'N3'!R15</f>
+      <c r="I12" s="27">
+        <f ca="1">'N3'!R10</f>
         <v>17.709880000000002</v>
       </c>
     </row>
@@ -3271,32 +3171,32 @@
       <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="C13" s="30">
-        <f>'N4'!L15</f>
+      <c r="C13" s="27">
+        <f ca="1">'N4'!L10</f>
         <v>2.5003799999999998</v>
       </c>
-      <c r="D13" s="30">
-        <f>'N4'!M15</f>
+      <c r="D13" s="27">
+        <f ca="1">'N4'!M10</f>
         <v>1.2528599999999999</v>
       </c>
-      <c r="E13" s="30">
-        <f>'N4'!N15</f>
+      <c r="E13" s="27">
+        <f ca="1">'N4'!N10</f>
         <v>26.216259999999998</v>
       </c>
-      <c r="F13" s="30">
-        <f>'N4'!O15</f>
+      <c r="F13" s="27">
+        <f ca="1">'N4'!O10</f>
         <v>6.1052400000000002</v>
       </c>
-      <c r="G13" s="30">
-        <f>'N4'!P15</f>
+      <c r="G13" s="27">
+        <f ca="1">'N4'!P10</f>
         <v>27.358699999999999</v>
       </c>
-      <c r="H13" s="30">
-        <f>'N4'!Q15</f>
+      <c r="H13" s="27">
+        <f ca="1">'N4'!Q10</f>
         <v>17.412479999999999</v>
       </c>
-      <c r="I13" s="30">
-        <f>'N4'!R15</f>
+      <c r="I13" s="27">
+        <f ca="1">'N4'!R10</f>
         <v>16.238660000000003</v>
       </c>
     </row>
@@ -3309,23 +3209,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="225bc2f8-bdb1-4394-a915-b064010f0aa2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003AAC2FDC759CDD4A90429900B1B6F585" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="32b7870d02875583ad3207b7f3f1dbe8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="225bc2f8-bdb1-4394-a915-b064010f0aa2" xmlns:ns4="603c0527-f966-4274-8677-990efa22e14b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="997dcc394722436272f8717eca1e188d" ns3:_="" ns4:_="">
     <xsd:import namespace="225bc2f8-bdb1-4394-a915-b064010f0aa2"/>
@@ -3558,10 +3441,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="225bc2f8-bdb1-4394-a915-b064010f0aa2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37BC1125-36FB-4455-B92A-BF66CEA6330F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CADE85A-AC40-44FD-AFAD-32B071BEDFA3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="225bc2f8-bdb1-4394-a915-b064010f0aa2"/>
+    <ds:schemaRef ds:uri="603c0527-f966-4274-8677-990efa22e14b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3584,20 +3495,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CADE85A-AC40-44FD-AFAD-32B071BEDFA3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37BC1125-36FB-4455-B92A-BF66CEA6330F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="225bc2f8-bdb1-4394-a915-b064010f0aa2"/>
-    <ds:schemaRef ds:uri="603c0527-f966-4274-8677-990efa22e14b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>